--- a/backend/test_codes/table_analyzer_codes/outputs2/b5_040_reconstructed.xlsx
+++ b/backend/test_codes/table_analyzer_codes/outputs2/b5_040_reconstructed.xlsx
@@ -437,76 +437,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>行标记</t>
         </is>
@@ -515,904 +521,997 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;(人民币百万元,百分 比除外)</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>(人民币百万元,百分 比除外)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>e a</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="M2" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>2024 年第四季度</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>2024 年第三季度</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>折算前数值</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>折算后数 折算前数值</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>折算后数 值</t>
         </is>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>无期限</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>&lt;6个月</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>6-12个月</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>&gt;1年</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>值 无期限</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>&lt;6个月</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>6-12个月</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>&gt;1年</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;资本</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>可用的稳定资金&gt;&gt;资本</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>资本</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>3,927,743</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>3,927,743</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>3,889,504</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>3,889,504</t>
         </is>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
+      <c r="M6" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;监管资本&gt;&gt;监管资本</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;监管资本</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>监管资本</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>3.927.743</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>3.927.743</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>3.889.504</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>3,889,504</t>
         </is>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="M7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;其他资本工具&gt;&gt;其他资本工具</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
+          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;其他资本工具</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>其他资本工具</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="n">
-        <v>0</v>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;来自零售和小企业客户 的存款</t>
+          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>来自零售和小企业客户 的存款</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>7,190,311</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>9,612,211</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>331,138</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>794,435</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>16,379.281 6,995,821</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>9,401,770</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>411,958</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>848,019</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>16,136,127</t>
         </is>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>稳定存款</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>3,264,551</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>18.430</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>8.069</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>6.568</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>3,133,065 3,165,392</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>17.357</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>7.508</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>6.950</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>3,037,695</t>
         </is>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>欠稳定存款</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>3.925.760</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>9.593.781</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>323.069</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>787.867</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>13.246.216 3,830,429</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>9,384.413</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>404.450</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>841.069</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>13.098.432</t>
         </is>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="M11" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>批发融资</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
           <t>1,750,282</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>13,221,187</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>1,755,405</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>851,151</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>7.523.964 2,616,549</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>13,066,185</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1,871,641</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>922,785</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>8,153,873</t>
         </is>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="M12" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>业务关系存款</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>1,592,324</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>5,196,931</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>48.978</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>3,419,123 2,453,200</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>5,152,424</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>75.039</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>3,840,335</t>
         </is>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="M13" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>其他批发融资</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t>157,958</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>8,024,256</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>1,706,427</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>851,145</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>4,104,841 163,349</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>7,913,761</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>1,796,602</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>922,781</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>4,313,538</t>
         </is>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="M14" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;相互依存的负债&gt;&gt;相互依存的负债</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr"/>
+          <t>可用的稳定资金&gt;&gt;相互依存的负债</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>相互依存的负债</t>
+        </is>
+      </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="n">
-        <v>0</v>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债&gt;&gt;其他负债</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="inlineStr">
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>其他负债</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>281,494</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>212,635</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>324,842</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>327,334</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>248,565</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>222,057</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>120,375</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>171,134</t>
         </is>
       </c>
-      <c r="L16" s="3" t="n">
-        <v>0</v>
+      <c r="M16" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;净稳定资金比例衍生产品负债&gt;&gt;净稳定资金比例衍 生产品负债</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr">
+          <t>可用的稳定资金&gt;&gt;净稳定资金比例衍生产品负债</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>净稳定资金比例衍 生产品负债</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>103,825</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>60.269</t>
         </is>
       </c>
-      <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
-        <v>0</v>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益&gt;&gt;以上未包括的所有 其它负债和权益</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr"/>
-      <c r="C18" s="3" t="inlineStr">
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>以上未包括的所有 其它负债和权益</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>281,494</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>212,635</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>221,017</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>327,334</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>248,565</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>222,057</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>60.106</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>171,134</t>
         </is>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>0</v>
+      <c r="M18" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;可用的稳定资金合计&gt;&gt;可用的稳定资金合计</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="3" t="n"/>
+          <t>可用的稳定资金&gt;&gt;可用的稳定资金合计</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>可用的稳定资金合计</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>28,158,322</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>28,350,638</t>
         </is>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>0</v>
+      <c r="M19" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产&gt;&gt;净稳定资金比例合格优 质流动性资产</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="n"/>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>净稳定资金比例合格优 质流动性资产</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>2,512,583</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="n"/>
+      <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>2,554,976</t>
         </is>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>0</v>
+      <c r="M20" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款&gt;&gt;存放在金融机构的业务 关系存款</t>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>存放在金融机构的业务 关系存款</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
           <t>51,698</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>17,931</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>7.484</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>2,673</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>41,448 64,428</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>33,752</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>3,059</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>2,734</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>53,624</t>
         </is>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="M21" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;贷款和证券&gt;&gt;贷款和证券</t>
+          <t>所需的稳定资金&gt;&gt;贷款和证券</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
+          <t>贷款和证券</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
           <t>1,132,786</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>6,941,603</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>3,570,517</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>16,039,685</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>17,683,465 1,091,884</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>7,224,215</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>3,380,129</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>16,096,481</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>17,678,317</t>
         </is>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="M22" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1453,6 +1552,9 @@
         <v>1</v>
       </c>
       <c r="L23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3" t="n">
         <v>1</v>
       </c>
     </row>
